--- a/Ejercicios/semana4/Prueba escritorio y diccionario.xlsx
+++ b/Ejercicios/semana4/Prueba escritorio y diccionario.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\Personal\Cesde\2026\Medellin\S2 - Medellin\2-Logica de Programación Grupo Uribe\Evidencias\Ejercicios\semana4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9AD7802-C095-432F-80A5-7EE45FEF7651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC907D7F-8F64-4527-B330-6530F1261F69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B8D7741F-C1F9-447B-BF38-A382103C8979}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B8D7741F-C1F9-447B-BF38-A382103C8979}"/>
   </bookViews>
   <sheets>
     <sheet name="Prueba escritorio" sheetId="1" r:id="rId1"/>
@@ -36,6 +36,65 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>USUARIO</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{DCF4288B-526F-4641-A782-5AAFDECB88C5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>USUARIO:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Aquí van los nombres de sus variables
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{C9D33EE8-9ADA-46A7-A33D-A469DE1BFE8E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>USUARIO:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Aquí va su algoritmo</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="31">
   <si>
@@ -136,7 +195,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -156,6 +215,19 @@
       <color theme="1"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -549,18 +621,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4362811-208A-4CE2-A963-4881D62BC06D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4362811-208A-4CE2-A963-4881D62BC06D}">
   <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="109.42578125" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" customWidth="1"/>
-    <col min="4" max="6" width="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" customWidth="1"/>
+    <col min="2" max="7" width="41.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="45" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -620,7 +689,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="42" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -640,7 +709,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="42" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -660,7 +729,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="42" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
@@ -680,7 +749,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="42" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
@@ -700,7 +769,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="42" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
@@ -720,7 +789,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="42" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -740,7 +809,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="42" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
@@ -760,7 +829,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="42" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -780,7 +849,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="42" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
@@ -883,6 +952,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
